--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.519</v>
+        <v>0.645</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>418.11</v>
+        <v>456.14</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.778</v>
+        <v>0.944</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04549000263214111</v>
+        <v>0.05238999843597412</v>
       </c>
     </row>
     <row r="6">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1.246</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="8">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>1094369804288</v>
+        <v>1068558516224</v>
       </c>
     </row>
     <row r="33">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>3383596154880</v>
+        <v>3518010228736</v>
       </c>
     </row>
     <row r="34">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473678.448256</v>
+        <v>5186474270.811593</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>418.11</v>
+        <v>456.14</v>
       </c>
     </row>
     <row r="38">
@@ -1508,208 +1508,206 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2168516509696</v>
+        <v>2365758373888</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>36.29</v>
+        <v>33.15</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.32</v>
+        <v>5.42</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>5347.TWO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>VANGUARD INTERNATIONAL SEMICOND</t>
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>454994329600</v>
+        <v>368960339968</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>54.063206</v>
+        <v>40.809628</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>50.888</v>
+        <v>22.148</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>16.262</v>
+        <v>7.314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>6770.TW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amkor Technology, Inc.</t>
+          <t>POWERCHIP SEMICONDUCTOR MANUFAC</t>
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>16498394112</v>
+        <v>343674683392</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>38.252872</v>
+        <v>22.42236</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.396</v>
+        <v>32.091</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.433</v>
+        <v>5.718</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>688249.SS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASML Holding N.V. - New York Re</t>
+          <t>NEXCHIP SEMICONDUCTOR CORPORATI</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>687444459520</v>
+        <v>67065966592</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>60.503223</v>
+        <v>93.78125</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>2992.094</v>
+        <v>17.722</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1128.219</v>
+        <v>7.211</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>688396.SS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASE Technology Holding Co., Ltd</t>
+          <t>CHINA RESOURCES MICROELECTRONIC</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>88372133888</v>
+        <v>69093523456</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>62.9375</v>
+        <v>65.8481</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>2.091</v>
+        <v>25.324</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.392</v>
+        <v>5.098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>688981.SS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>SEMICONDUCTOR MANUFACTURING INT</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1865447243776</v>
+        <v>916855980032</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>65.45910000000001</v>
+        <v>117.67033</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>45.065</v>
+        <v>176.194</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>25.131</v>
+        <v>89.642</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DIOD</t>
+          <t>HHUSF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diodes Incorporated</t>
+          <t>HUA HONG GRACE SEMICONDUCTOR LT</t>
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>4356020224</v>
+        <v>33057861632</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>51.248646</v>
+        <v>235.83333</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>20.859</v>
+        <v>35.491</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.657</v>
+        <v>10.013</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>411637972992</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>62.10566</v>
-      </c>
+        <v>560590880768</v>
+      </c>
+      <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>55.023</v>
+        <v>36.044</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>19.916</v>
+        <v>10.643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSEM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Tower Semiconductor Ltd.</t>
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1710592753664</v>
+        <v>25409423360</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>24.504728</v>
+        <v>88.85375999999999</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>15.402</v>
+        <v>44.732</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>7.832</v>
+        <v>15.621</v>
       </c>
     </row>
     <row r="15">
@@ -1757,13 +1755,13 @@
         </is>
       </c>
       <c r="D17" s="35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="n">
-        <v>0.167</v>
-      </c>
       <c r="F17" s="35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.645</v>
+        <v>0.648</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>456.14</v>
+        <v>451.15</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.046</v>
+        <v>0.055</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05238999843597412</v>
+        <v>0.05245999813079834</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186474270.811593</v>
+        <v>5186473862.795079</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>456.14</v>
+        <v>451.15</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2365758373888</v>
+        <v>2339877683200</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>33.15</v>
+        <v>32.79</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.42</v>
+        <v>5.24</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.87</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="6">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>67065966592</v>
+        <v>66954227712</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>93.78125</v>
+        <v>93.625</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>17.722</v>
+        <v>17.701</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>7.211</v>
+        <v>7.202</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>69093523456</v>
+        <v>68934139904</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>65.8481</v>
+        <v>65.69620500000001</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>25.324</v>
+        <v>25.258</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>5.098</v>
+        <v>5.085</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>916855980032</v>
+        <v>928329498624</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>117.67033</v>
+        <v>119.14285</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>176.194</v>
+        <v>178.366</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>89.642</v>
+        <v>90.747</v>
       </c>
     </row>
     <row r="11">
@@ -1676,14 +1676,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>560590880768</v>
+        <v>557816217600</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>36.044</v>
+        <v>34.235</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>10.643</v>
+        <v>10.109</v>
       </c>
     </row>
     <row r="13">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>25409423360</v>
+        <v>25721389056</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>88.85375999999999</v>
+        <v>89.944664</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>44.732</v>
+        <v>41.04</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>15.621</v>
+        <v>14.332</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.648</v>
+        <v>0.646</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>451.15</v>
+        <v>453.31</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05245999813079834</v>
+        <v>0.0524399995803833</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473862.795079</v>
+        <v>5186473731.0891</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>451.15</v>
+        <v>453.31</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2339877683200</v>
+        <v>2351080407040</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>32.79</v>
+        <v>32.94</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="6">
@@ -1676,14 +1676,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>557816217600</v>
+        <v>553455190016</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>34.235</v>
+        <v>33.522</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>10.109</v>
+        <v>9.898</v>
       </c>
     </row>
     <row r="13">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>25721389056</v>
+        <v>25851375616</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>89.944664</v>
+        <v>90.399216</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>41.04</v>
+        <v>41.032</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>14.332</v>
+        <v>14.329</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.646</v>
+        <v>0.651</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>453.31</v>
+        <v>446.56</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.051</v>
+        <v>0.064</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0524399995803833</v>
+        <v>0.05240000247955322</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473731.0891</v>
+        <v>5186474073.522035</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>453.31</v>
+        <v>446.56</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2351080407040</v>
+        <v>2316071862272</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>32.94</v>
+        <v>32.45</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>5.18</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>368960339968</v>
+        <v>358079463424</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>40.809628</v>
+        <v>39.606125</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>22.148</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>343674683392</v>
+        <v>339866681344</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.42236</v>
+        <v>22.173914</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>32.091</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>66954227712</v>
+        <v>65300484096</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>93.625</v>
+        <v>91.3125</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>17.701</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>68934139904</v>
+        <v>66609766400</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>65.69620500000001</v>
+        <v>63.481014</v>
       </c>
       <c r="E9" s="33" t="n">
         <v>25.258</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>928329498624</v>
+        <v>913431003136</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>119.14285</v>
+        <v>117.23077</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>178.366</v>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>553455190016</v>
+        <v>535588175872</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>25851375616</v>
+        <v>24070002688</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>90.399216</v>
+        <v>84.16996</v>
       </c>
       <c r="E13" s="33" t="n">
         <v>41.032</v>

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-12 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.651</v>
+        <v>0.653</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>446.56</v>
+        <v>442.085</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.064</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05240000247955322</v>
+        <v>0.05220999717712402</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186474073.522035</v>
+        <v>5186474137.19986</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>446.56</v>
+        <v>442.085</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2316071862272</v>
+        <v>2292862418944</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>32.45</v>
+        <v>32.13</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.18</v>
+        <v>5.06</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>358079463424</v>
+        <v>346209419264</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>39.606125</v>
+        <v>37.154987</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>22.148</v>
+        <v>20.883</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>7.314</v>
+        <v>6.896</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>339866681344</v>
+        <v>321302528000</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.173914</v>
+        <v>20.70552</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>32.091</v>
+        <v>29.84</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>5.718</v>
+        <v>5.317</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>65300484096</v>
+        <v>65255792640</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>91.3125</v>
+        <v>88.48484999999999</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>17.701</v>
+        <v>17.389</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>7.202</v>
+        <v>7.076</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>66609766400</v>
+        <v>66171457536</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>63.481014</v>
+        <v>61.506172</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>25.258</v>
+        <v>24.111</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>5.085</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>913431003136</v>
+        <v>907608588288</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>117.23077</v>
+        <v>115.21739</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>178.366</v>
+        <v>174.444</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>90.747</v>
+        <v>88.751</v>
       </c>
     </row>
     <row r="11">
@@ -1676,14 +1676,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>535588175872</v>
+        <v>538363363328</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>33.522</v>
+        <v>32.519</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>9.898</v>
+        <v>9.602</v>
       </c>
     </row>
     <row r="13">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>24070002688</v>
+        <v>24524388352</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>84.16996</v>
+        <v>85.75889599999999</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>41.032</v>
+        <v>38.721</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>14.329</v>
+        <v>13.522</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.653</v>
+        <v>0.66</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>442.085</v>
+        <v>430.385</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186474137.19986</v>
+        <v>5186473830.15672</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>442.085</v>
+        <v>430.385</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2292862418944</v>
+        <v>2232180539392</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>32.13</v>
+        <v>31.28</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>346209419264</v>
+        <v>348187754496</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>37.154987</v>
+        <v>38.512035</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>20.883</v>
+        <v>20.993</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>6.896</v>
+        <v>6.933</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>321302528000</v>
+        <v>337962663936</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>20.70552</v>
+        <v>22.049688</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>29.84</v>
+        <v>31.516</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>5.317</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>65255792640</v>
+        <v>63400919040</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>88.48484999999999</v>
+        <v>88.65626</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>17.389</v>
+        <v>17.048</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>7.076</v>
+        <v>6.937</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>66171457536</v>
+        <v>64232267776</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>61.506172</v>
+        <v>61.21519</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>24.111</v>
+        <v>23.306</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>4.854</v>
+        <v>4.692</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>907608588288</v>
+        <v>878072299520</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>115.21739</v>
+        <v>112.69231</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>174.444</v>
+        <v>168.852</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>88.751</v>
+        <v>85.90600000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1676,14 +1676,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>538363363328</v>
+        <v>521579462656</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>32.519</v>
+        <v>32.956</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>9.602</v>
+        <v>9.731</v>
       </c>
     </row>
     <row r="13">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>24524388352</v>
+        <v>23756341248</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>85.75889599999999</v>
+        <v>83.07313000000001</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>38.721</v>
+        <v>39.8</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>13.522</v>
+        <v>13.899</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TSM_research.xlsx
+++ b/app/reports/TSM_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.66</v>
+        <v>0.658</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>430.385</v>
+        <v>419.96</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.093</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05220999717712402</v>
+        <v>0.05085000038146972</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>5186473830.15672</v>
+        <v>5186474034.327079</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>430.385</v>
+        <v>419.96</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>2232180539392</v>
+        <v>2178111635456</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>31.28</v>
+        <v>31.6</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>5.07</v>
+        <v>4.87</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>348187754496</v>
+        <v>319501828096</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>38.512035</v>
+        <v>35.33917</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>20.993</v>
+        <v>19.398</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>6.933</v>
+        <v>6.406</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>337962663936</v>
+        <v>315114455040</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.049688</v>
+        <v>20.559006</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>31.516</v>
+        <v>29.217</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>5.616</v>
+        <v>5.206</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>63400919040</v>
+        <v>61702479872</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>88.65626</v>
+        <v>86.28126</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>17.048</v>
+        <v>16.736</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>6.937</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="9">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>64232267776</v>
+        <v>64577601536</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>61.21519</v>
+        <v>61.5443</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>23.306</v>
+        <v>23.449</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>4.692</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="10">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>878072299520</v>
+        <v>894255169536</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>112.69231</v>
+        <v>114.76923</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>168.852</v>
+        <v>171.916</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>85.90600000000001</v>
+        <v>87.465</v>
       </c>
     </row>
     <row r="11">
@@ -1658,10 +1658,10 @@
         <v>235.83333</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>35.491</v>
+        <v>28.464</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>10.013</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1676,14 +1676,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>521579462656</v>
+        <v>498453282816</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>32.956</v>
+        <v>31.552</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>9.731</v>
+        <v>9.316000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>23756341248</v>
+        <v>23195142144</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>83.07313000000001</v>
+        <v>86.22269</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>39.8</v>
+        <v>37.331</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>13.899</v>
+        <v>13.037</v>
       </c>
     </row>
     <row r="15">
